--- a/tests/SAMPLE_Lenovo_Inventory_SYNTH.xlsx
+++ b/tests/SAMPLE_Lenovo_Inventory_SYNTH.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -18109,7 +18109,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
@@ -19441,7 +19441,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -19498,7 +19498,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -19572,7 +19572,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -22093,7 +22093,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
@@ -22332,7 +22332,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -22759,7 +22759,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -24011,7 +24011,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -24085,7 +24085,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
@@ -25172,7 +25172,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -25889,7 +25889,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -26509,7 +26509,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -26566,7 +26566,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P362" t="inlineStr">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -27010,7 +27010,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P368" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -27306,7 +27306,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -28336,7 +28336,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -28393,7 +28393,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -29002,7 +29002,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P396" t="inlineStr">
@@ -29201,7 +29201,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -29622,7 +29622,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P405" t="inlineStr">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P406" t="inlineStr">
@@ -30043,7 +30043,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -30265,7 +30265,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -30595,7 +30595,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P418" t="inlineStr">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -30743,7 +30743,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P420" t="inlineStr">
@@ -30834,7 +30834,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -30982,7 +30982,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -31130,7 +31130,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -32000,7 +32000,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -32057,7 +32057,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -33161,7 +33161,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -33457,7 +33457,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -33514,7 +33514,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P459" t="inlineStr">
@@ -33679,7 +33679,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -33901,7 +33901,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -33975,7 +33975,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -34123,7 +34123,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -34937,7 +34937,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -35415,7 +35415,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P485" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -36001,7 +36001,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -36075,7 +36075,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -36519,7 +36519,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -36576,7 +36576,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P501" t="inlineStr">
@@ -37657,7 +37657,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -37805,7 +37805,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -37862,7 +37862,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P519" t="inlineStr">
@@ -38101,7 +38101,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -38158,7 +38158,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P523" t="inlineStr">
@@ -38522,7 +38522,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -38744,7 +38744,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -38818,7 +38818,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -39290,7 +39290,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -39347,7 +39347,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P540" t="inlineStr">
@@ -39364,7 +39364,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -40030,7 +40030,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -40400,7 +40400,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -40844,7 +40844,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -41436,7 +41436,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -41584,7 +41584,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -41641,7 +41641,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P571" t="inlineStr">
@@ -41732,7 +41732,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -41931,7 +41931,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -42079,7 +42079,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -42967,7 +42967,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -43115,7 +43115,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -43263,7 +43263,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -43320,7 +43320,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P594" t="inlineStr">
@@ -43411,7 +43411,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -44070,7 +44070,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -44176,7 +44176,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -44400,7 +44400,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -44456,7 +44456,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -44512,7 +44512,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -44556,7 +44556,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -44951,7 +44951,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -44995,7 +44995,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -45319,7 +45319,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45331,7 +45331,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -45667,7 +45667,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -45711,7 +45711,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45891,7 +45891,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -46218,7 +46218,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -46330,7 +46330,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -46386,7 +46386,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -46495,7 +46495,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -46539,7 +46539,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -46825,7 +46825,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -47214,7 +47214,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -47258,7 +47258,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -47314,7 +47314,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47326,7 +47326,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47382,7 +47382,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -47426,7 +47426,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -48142,7 +48142,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -48773,7 +48773,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -49263,7 +49263,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -49570,7 +49570,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -51072,7 +51072,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51340,7 +51340,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -51366,7 +51366,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51421,7 +51421,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -51512,7 +51512,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -51548,7 +51548,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51560,7 +51560,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -51988,7 +51988,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Silver Isle Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -52100,7 +52100,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/tests/SAMPLE_Lenovo_Inventory_SYNTH.xlsx
+++ b/tests/SAMPLE_Lenovo_Inventory_SYNTH.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8589,7 +8589,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9033,7 +9033,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9090,7 +9090,7 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9505,7 +9505,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9579,7 +9579,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P127" t="inlineStr">
@@ -10097,7 +10097,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -11013,7 +11013,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -11087,7 +11087,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -11383,7 +11383,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P152" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -13312,7 +13312,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -13460,7 +13460,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -13591,7 +13591,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -14399,7 +14399,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -15042,7 +15042,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
@@ -15560,7 +15560,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -15617,7 +15617,7 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -17028,7 +17028,7 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P230" t="inlineStr">
@@ -17961,7 +17961,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -18109,7 +18109,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -18701,7 +18701,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="O263" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P263" t="inlineStr">
@@ -19441,7 +19441,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -19498,7 +19498,7 @@
       </c>
       <c r="O264" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P264" t="inlineStr">
@@ -19515,7 +19515,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -19572,7 +19572,7 @@
       </c>
       <c r="O265" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
@@ -19589,7 +19589,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="O266" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
@@ -19959,7 +19959,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -21393,7 +21393,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="O291" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P291" t="inlineStr">
@@ -21541,7 +21541,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P293" t="inlineStr">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -22093,7 +22093,7 @@
       </c>
       <c r="O300" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P300" t="inlineStr">
@@ -22332,7 +22332,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -22480,7 +22480,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -22759,7 +22759,7 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -23072,7 +23072,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -23715,7 +23715,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -23863,7 +23863,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -24011,7 +24011,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -24085,7 +24085,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -24142,7 +24142,7 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
@@ -25172,7 +25172,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -25741,7 +25741,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="O351" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P351" t="inlineStr">
@@ -25889,7 +25889,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -26509,7 +26509,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -26566,7 +26566,7 @@
       </c>
       <c r="O362" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P362" t="inlineStr">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -27010,7 +27010,7 @@
       </c>
       <c r="O368" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P368" t="inlineStr">
@@ -27249,7 +27249,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -27306,7 +27306,7 @@
       </c>
       <c r="O372" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P372" t="inlineStr">
@@ -27619,7 +27619,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -28336,7 +28336,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -28393,7 +28393,7 @@
       </c>
       <c r="O387" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P387" t="inlineStr">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -29002,7 +29002,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -29059,7 +29059,7 @@
       </c>
       <c r="O396" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P396" t="inlineStr">
@@ -29201,7 +29201,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -29349,7 +29349,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -29622,7 +29622,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -29679,7 +29679,7 @@
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P405" t="inlineStr">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -29753,7 +29753,7 @@
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P406" t="inlineStr">
@@ -30043,7 +30043,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -30265,7 +30265,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -30538,7 +30538,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -30595,7 +30595,7 @@
       </c>
       <c r="O418" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P418" t="inlineStr">
@@ -30686,7 +30686,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -30743,7 +30743,7 @@
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P420" t="inlineStr">
@@ -30834,7 +30834,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -30982,7 +30982,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -31130,7 +31130,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -32000,7 +32000,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -32057,7 +32057,7 @@
       </c>
       <c r="O439" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P439" t="inlineStr">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -33161,7 +33161,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -33457,7 +33457,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -33514,7 +33514,7 @@
       </c>
       <c r="O459" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P459" t="inlineStr">
@@ -33679,7 +33679,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -33901,7 +33901,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -33975,7 +33975,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -34123,7 +34123,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -34937,7 +34937,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -35358,7 +35358,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -35415,7 +35415,7 @@
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P485" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -36001,7 +36001,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -36075,7 +36075,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -36519,7 +36519,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -36576,7 +36576,7 @@
       </c>
       <c r="O501" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P501" t="inlineStr">
@@ -37657,7 +37657,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -37805,7 +37805,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -37862,7 +37862,7 @@
       </c>
       <c r="O519" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P519" t="inlineStr">
@@ -38101,7 +38101,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -38158,7 +38158,7 @@
       </c>
       <c r="O523" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P523" t="inlineStr">
@@ -38522,7 +38522,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -38744,7 +38744,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -38818,7 +38818,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -39290,7 +39290,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -39347,7 +39347,7 @@
       </c>
       <c r="O540" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P540" t="inlineStr">
@@ -39364,7 +39364,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -39512,7 +39512,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -40030,7 +40030,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -40400,7 +40400,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -40844,7 +40844,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
@@ -41436,7 +41436,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -41584,7 +41584,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -41641,7 +41641,7 @@
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P571" t="inlineStr">
@@ -41732,7 +41732,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
@@ -41931,7 +41931,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C576" t="inlineStr">
@@ -42079,7 +42079,7 @@
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
@@ -42967,7 +42967,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -43115,7 +43115,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -43263,7 +43263,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -43320,7 +43320,7 @@
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
       <c r="P594" t="inlineStr">
@@ -43411,7 +43411,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -44070,7 +44070,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -44176,7 +44176,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -44400,7 +44400,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -44456,7 +44456,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -44512,7 +44512,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -44556,7 +44556,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -44951,7 +44951,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -44995,7 +44995,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45116,7 +45116,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -45275,7 +45275,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -45319,7 +45319,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45331,7 +45331,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -45667,7 +45667,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -45711,7 +45711,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -45891,7 +45891,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -46218,7 +46218,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -46330,7 +46330,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -46386,7 +46386,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -46495,7 +46495,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -46539,7 +46539,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -46825,7 +46825,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -47214,7 +47214,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -47258,7 +47258,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47270,7 +47270,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -47314,7 +47314,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47326,7 +47326,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -47370,7 +47370,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -47382,7 +47382,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -47426,7 +47426,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -48142,7 +48142,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -48773,7 +48773,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -49263,7 +49263,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -49570,7 +49570,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -51072,7 +51072,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -51103,7 +51103,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51340,7 +51340,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -51366,7 +51366,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51421,7 +51421,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -51512,7 +51512,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -51548,7 +51548,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>12 Narra Lane, Pasig</t>
+          <t>12 Sample Lane, Sample City</t>
         </is>
       </c>
     </row>
@@ -51560,7 +51560,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>St. Vincent Ferrer Academy</t>
+          <t>Sample Ferrer Academy</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -51988,7 +51988,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Isidro Integrated School</t>
+          <t>Sample Integrated School</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -52100,7 +52100,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Corpus Christi College</t>
+          <t>Sample Christi College</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
